--- a/Excel/AbyssConfig.xlsx
+++ b/Excel/AbyssConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
@@ -40,7 +40,10 @@
     <t>ItemId</t>
   </si>
   <si>
-    <t>SetId</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Quality</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,13 +67,13 @@
     <t>double[]</t>
   </si>
   <si>
-    <t>血怨魔刃</t>
-  </si>
-  <si>
-    <t>2001,2003,2013,95</t>
-  </si>
-  <si>
-    <t>1,1,1,1</t>
+    <t>血怨魔刀</t>
+  </si>
+  <si>
+    <t>2001,2003,2007,94</t>
+  </si>
+  <si>
+    <t>1,2,1,0.1</t>
   </si>
   <si>
     <t>血怨魔甲</t>
@@ -79,12 +82,21 @@
     <t>血怨魔链</t>
   </si>
   <si>
+    <t>2001,2003,2007,91</t>
+  </si>
+  <si>
     <t>血怨魔盔</t>
   </si>
   <si>
+    <t>2001,2003,2007,92</t>
+  </si>
+  <si>
     <t>血怨魔镯</t>
   </si>
   <si>
+    <t>2001,2003,2007,93</t>
+  </si>
+  <si>
     <t>血怨魔戒</t>
   </si>
   <si>
@@ -94,21 +106,33 @@
     <t>血怨魔靴</t>
   </si>
   <si>
-    <t>碎魂魔刃</t>
-  </si>
-  <si>
-    <t>碎魂魔甲</t>
+    <t>碎魂魔杖</t>
+  </si>
+  <si>
+    <t>2001,2003,2008,94</t>
+  </si>
+  <si>
+    <t>碎魂魔衣</t>
   </si>
   <si>
     <t>碎魂魔链</t>
   </si>
   <si>
+    <t>2001,2003,2008,91</t>
+  </si>
+  <si>
     <t>碎魂魔盔</t>
   </si>
   <si>
+    <t>2001,2003,2008,92</t>
+  </si>
+  <si>
     <t>碎魂魔镯</t>
   </si>
   <si>
+    <t>2001,2003,2008,93</t>
+  </si>
+  <si>
     <t>碎魂魔戒</t>
   </si>
   <si>
@@ -118,19 +142,31 @@
     <t>碎魂魔靴</t>
   </si>
   <si>
-    <t>哀嚎魔刃</t>
-  </si>
-  <si>
-    <t>哀嚎魔甲</t>
+    <t>哀嚎魔剑</t>
+  </si>
+  <si>
+    <t>2001,2003,2009,94</t>
+  </si>
+  <si>
+    <t>哀嚎魔袍</t>
   </si>
   <si>
     <t>哀嚎魔链</t>
   </si>
   <si>
+    <t>2001,2003,2009,91</t>
+  </si>
+  <si>
     <t>哀嚎魔盔</t>
   </si>
   <si>
+    <t>2001,2003,2009,92</t>
+  </si>
+  <si>
     <t>哀嚎魔镯</t>
+  </si>
+  <si>
+    <t>2001,2003,2009,93</t>
   </si>
   <si>
     <t>哀嚎魔戒</t>
@@ -1122,19 +1158,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:H31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="C3:I31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="9.41666666666667" style="1"/>
-    <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.8333333333333" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1153,8 +1189,11 @@
       <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1173,16 +1212,19 @@
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
@@ -1193,8 +1235,11 @@
       <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1204,17 +1249,20 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="1">
+        <v>7</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="I6" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1224,17 +1272,20 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="F7" s="1">
+        <v>7</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="I7" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1244,17 +1295,20 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F8" s="1">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1264,17 +1318,20 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F9" s="1">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1284,17 +1341,20 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F10" s="1">
+        <v>7</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1304,17 +1364,20 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F11" s="1">
+        <v>7</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1324,17 +1387,20 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1">
+        <v>7</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="I12" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1344,17 +1410,20 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1364,17 +1433,20 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="F14" s="1">
+        <v>7</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1384,17 +1456,20 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:8">
+      <c r="F15" s="1">
+        <v>7</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:9">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1402,19 +1477,22 @@
         <v>70000013</v>
       </c>
       <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>7</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:9">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1422,19 +1500,22 @@
         <v>70000014</v>
       </c>
       <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>7</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:9">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1442,19 +1523,22 @@
         <v>70000015</v>
       </c>
       <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>7</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:9">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1462,19 +1546,22 @@
         <v>70000016</v>
       </c>
       <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>7</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:9">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1482,19 +1569,22 @@
         <v>70000017</v>
       </c>
       <c r="E20" s="1">
-        <v>2</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>7</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:9">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1502,19 +1592,22 @@
         <v>70000018</v>
       </c>
       <c r="E21" s="1">
-        <v>2</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>7</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:9">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1522,19 +1615,22 @@
         <v>70000021</v>
       </c>
       <c r="E22" s="1">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>7</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:9">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1542,19 +1638,22 @@
         <v>70000022</v>
       </c>
       <c r="E23" s="1">
-        <v>2</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>7</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:9">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1562,19 +1661,22 @@
         <v>70000023</v>
       </c>
       <c r="E24" s="1">
-        <v>2</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>7</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:9">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1582,19 +1684,22 @@
         <v>70000024</v>
       </c>
       <c r="E25" s="1">
-        <v>2</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>7</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:9">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -1602,19 +1707,22 @@
         <v>70000025</v>
       </c>
       <c r="E26" s="1">
-        <v>3</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>7</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:9">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1622,19 +1730,22 @@
         <v>70000026</v>
       </c>
       <c r="E27" s="1">
-        <v>3</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>7</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:9">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -1642,19 +1753,22 @@
         <v>70000027</v>
       </c>
       <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>7</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:9">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -1662,27 +1776,30 @@
         <v>70000028</v>
       </c>
       <c r="E29" s="1">
-        <v>3</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:8">
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:8">
-      <c r="H31" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>7</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:9">
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:9">
+      <c r="I31" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AbyssConfig.xlsx
+++ b/Excel/AbyssConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
   <si>
     <t>Id</t>
   </si>
@@ -70,10 +70,10 @@
     <t>血怨魔刀</t>
   </si>
   <si>
-    <t>2001,2003,2007,94</t>
-  </si>
-  <si>
-    <t>1,2,1,0.1</t>
+    <t>2001,2003,2004,2007,94</t>
+  </si>
+  <si>
+    <t>1,2,1,1,0.1</t>
   </si>
   <si>
     <t>血怨魔甲</t>
@@ -82,19 +82,22 @@
     <t>血怨魔链</t>
   </si>
   <si>
-    <t>2001,2003,2007,91</t>
+    <t>2001,2003,2004,2007,91</t>
+  </si>
+  <si>
+    <t>1,2,1,1,0.15</t>
   </si>
   <si>
     <t>血怨魔盔</t>
   </si>
   <si>
-    <t>2001,2003,2007,92</t>
+    <t>2001,2003,2004,2007,92</t>
   </si>
   <si>
     <t>血怨魔镯</t>
   </si>
   <si>
-    <t>2001,2003,2007,93</t>
+    <t>2001,2003,2004,2007,93</t>
   </si>
   <si>
     <t>血怨魔戒</t>
@@ -109,7 +112,7 @@
     <t>碎魂魔杖</t>
   </si>
   <si>
-    <t>2001,2003,2008,94</t>
+    <t>2001,2003,2005,2008,94</t>
   </si>
   <si>
     <t>碎魂魔衣</t>
@@ -118,19 +121,19 @@
     <t>碎魂魔链</t>
   </si>
   <si>
-    <t>2001,2003,2008,91</t>
+    <t>2001,2003,2005,2008,91</t>
   </si>
   <si>
     <t>碎魂魔盔</t>
   </si>
   <si>
-    <t>2001,2003,2008,92</t>
+    <t>2001,2003,2005,2008,92</t>
   </si>
   <si>
     <t>碎魂魔镯</t>
   </si>
   <si>
-    <t>2001,2003,2008,93</t>
+    <t>2001,2003,2005,2008,93</t>
   </si>
   <si>
     <t>碎魂魔戒</t>
@@ -145,7 +148,7 @@
     <t>哀嚎魔剑</t>
   </si>
   <si>
-    <t>2001,2003,2009,94</t>
+    <t>2001,2003,2006,2009,94</t>
   </si>
   <si>
     <t>哀嚎魔袍</t>
@@ -154,19 +157,19 @@
     <t>哀嚎魔链</t>
   </si>
   <si>
-    <t>2001,2003,2009,91</t>
+    <t>2001,2003,2006,2009,91</t>
   </si>
   <si>
     <t>哀嚎魔盔</t>
   </si>
   <si>
-    <t>2001,2003,2009,92</t>
+    <t>2001,2003,2006,2009,92</t>
   </si>
   <si>
     <t>哀嚎魔镯</t>
   </si>
   <si>
-    <t>2001,2003,2009,93</t>
+    <t>2001,2003,2006,2009,93</t>
   </si>
   <si>
     <t>哀嚎魔戒</t>
@@ -1305,7 +1308,7 @@
         <v>16</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1322,13 +1325,13 @@
         <v>7</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1345,13 +1348,13 @@
         <v>7</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1368,13 +1371,13 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1391,13 +1394,13 @@
         <v>7</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1414,13 +1417,13 @@
         <v>7</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -1437,10 +1440,10 @@
         <v>7</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>13</v>
@@ -1460,10 +1463,10 @@
         <v>7</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>13</v>
@@ -1483,13 +1486,13 @@
         <v>7</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:9">
@@ -1506,13 +1509,13 @@
         <v>7</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:9">
@@ -1529,13 +1532,13 @@
         <v>7</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:9">
@@ -1552,13 +1555,13 @@
         <v>7</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:9">
@@ -1575,13 +1578,13 @@
         <v>7</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:9">
@@ -1598,13 +1601,13 @@
         <v>7</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:9">
@@ -1621,10 +1624,10 @@
         <v>7</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>13</v>
@@ -1644,10 +1647,10 @@
         <v>7</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>13</v>
@@ -1667,13 +1670,13 @@
         <v>7</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:9">
@@ -1690,13 +1693,13 @@
         <v>7</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:9">
@@ -1713,13 +1716,13 @@
         <v>7</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:9">
@@ -1736,13 +1739,13 @@
         <v>7</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:9">
@@ -1759,13 +1762,13 @@
         <v>7</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:9">
@@ -1782,13 +1785,13 @@
         <v>7</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:9">
